--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N101_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N101_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.08368581775082</v>
+        <v>3.751098945384509</v>
       </c>
       <c r="D2" t="n">
-        <v>22.57969217131126</v>
+        <v>3.66919997783808</v>
       </c>
       <c r="E2" t="n">
-        <v>6.009479044572072</v>
+        <v>0.9765403447429618</v>
       </c>
       <c r="F2" t="n">
-        <v>5.991354180825635</v>
+        <v>0.9735950543841656</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.30182534874792</v>
+        <v>2.649046619171536</v>
       </c>
       <c r="D3" t="n">
-        <v>14.90180220470954</v>
+        <v>2.421542858265301</v>
       </c>
       <c r="E3" t="n">
-        <v>6.009479044572072</v>
+        <v>0.9765403447429618</v>
       </c>
       <c r="F3" t="n">
-        <v>5.991354180825635</v>
+        <v>0.9735950543841656</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.16927363300832</v>
+        <v>3.765006965363852</v>
       </c>
       <c r="D4" t="n">
-        <v>21.87499685804223</v>
+        <v>3.554686989431862</v>
       </c>
       <c r="E4" t="n">
-        <v>6.009479044572072</v>
+        <v>0.9765403447429618</v>
       </c>
       <c r="F4" t="n">
-        <v>5.991354180825635</v>
+        <v>0.9735950543841656</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.1479947317311</v>
+        <v>5.386549143906303</v>
       </c>
       <c r="D5" t="n">
-        <v>31.76109941581332</v>
+        <v>5.161178655069665</v>
       </c>
       <c r="E5" t="n">
-        <v>6.009479044572072</v>
+        <v>0.9765403447429618</v>
       </c>
       <c r="F5" t="n">
-        <v>5.991354180825635</v>
+        <v>0.9735950543841656</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
